--- a/gestao_projetos/modelos/relatorios-atividades-cabecalhos.xlsx
+++ b/gestao_projetos/modelos/relatorios-atividades-cabecalhos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ARGUS\gestao_projetos\modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB44A3B-5F6D-44DB-94B8-E9303DC2E44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB629FA-7E7E-4DED-BFA9-DE017E81F0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{103697AE-3D62-4C42-BEB7-9F07A5C2C0BD}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="143">
   <si>
     <t>01/02/27 a 26/02/27</t>
   </si>
@@ -515,12 +515,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -537,7 +543,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -564,6 +570,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3448,20 +3460,19 @@
     <col min="1" max="1" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="31" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" style="1" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="24.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="26" style="1" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -3687,7 +3698,7 @@
         <v>1</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3697,13 +3708,13 @@
       <c r="B5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="11" t="s">
         <v>102</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -3712,7 +3723,7 @@
       <c r="G5" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="11" t="s">
         <v>99</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -3721,19 +3732,19 @@
       <c r="J5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="11">
         <v>160</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="11">
         <v>4</v>
       </c>
       <c r="M5" s="1">
         <v>8</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="12">
         <v>2800</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="11" t="s">
         <v>43</v>
       </c>
       <c r="P5" s="1">
@@ -3742,6 +3753,9 @@
       <c r="Q5" s="1">
         <v>2</v>
       </c>
+      <c r="R5" s="11" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -4120,7 +4134,7 @@
         <v>1</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -4175,6 +4189,9 @@
       <c r="Q13" s="1">
         <v>2</v>
       </c>
+      <c r="R13" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -4606,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -4661,6 +4678,9 @@
       <c r="Q22" s="1">
         <v>2</v>
       </c>
+      <c r="R22" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -5092,7 +5112,7 @@
         <v>1</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -5147,6 +5167,9 @@
       <c r="Q31" s="1">
         <v>2</v>
       </c>
+      <c r="R31" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -5578,7 +5601,7 @@
         <v>1</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -5633,6 +5656,9 @@
       <c r="Q40" s="1">
         <v>2</v>
       </c>
+      <c r="R40" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -6064,7 +6090,7 @@
         <v>1</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
@@ -6119,6 +6145,9 @@
       <c r="Q49" s="1">
         <v>2</v>
       </c>
+      <c r="R49" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
@@ -6494,7 +6523,7 @@
         <v>1</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
@@ -6550,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
@@ -6605,6 +6634,9 @@
       <c r="Q58" s="1">
         <v>2</v>
       </c>
+      <c r="R58" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
@@ -6980,7 +7012,7 @@
         <v>1</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
@@ -7035,6 +7067,9 @@
       <c r="Q66" s="1">
         <v>1</v>
       </c>
+      <c r="R66" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
@@ -7088,6 +7123,9 @@
       <c r="Q67" s="1">
         <v>2</v>
       </c>
+      <c r="R67" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
@@ -7463,7 +7501,7 @@
         <v>1</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -7518,6 +7556,9 @@
       <c r="Q75" s="1">
         <v>1</v>
       </c>
+      <c r="R75" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
@@ -7893,7 +7934,7 @@
         <v>1</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -7948,6 +7989,9 @@
       <c r="Q83" s="1">
         <v>1</v>
       </c>
+      <c r="R83" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
@@ -8001,6 +8045,9 @@
       <c r="Q84" s="1">
         <v>2</v>
       </c>
+      <c r="R84" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
@@ -8376,7 +8423,7 @@
         <v>1</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
@@ -8431,6 +8478,9 @@
       <c r="Q92" s="1">
         <v>1</v>
       </c>
+      <c r="R92" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
@@ -8484,6 +8534,9 @@
       <c r="Q93" s="1">
         <v>2</v>
       </c>
+      <c r="R93" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
@@ -8859,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
@@ -8914,6 +8967,9 @@
       <c r="Q101" s="1">
         <v>1</v>
       </c>
+      <c r="R101" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
@@ -8967,6 +9023,9 @@
       <c r="Q102" s="1">
         <v>2</v>
       </c>
+      <c r="R102" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
@@ -9398,7 +9457,7 @@
         <v>1</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
@@ -9452,6 +9511,9 @@
       </c>
       <c r="Q111" s="1">
         <v>2</v>
+      </c>
+      <c r="R111" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">

--- a/gestao_projetos/modelos/relatorios-atividades-cabecalhos.xlsx
+++ b/gestao_projetos/modelos/relatorios-atividades-cabecalhos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ARGUS\gestao_projetos\modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB629FA-7E7E-4DED-BFA9-DE017E81F0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD1C01A-7D54-4656-9603-450BD6F02FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{103697AE-3D62-4C42-BEB7-9F07A5C2C0BD}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="140">
   <si>
     <t>01/02/27 a 26/02/27</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Sandro Haiden Teixeira</t>
   </si>
   <si>
-    <t>15338-9:EMBRAPII</t>
-  </si>
-  <si>
     <t>0002/2026</t>
   </si>
   <si>
@@ -90,18 +87,12 @@
     <t>02/11/26 a 30/11/26</t>
   </si>
   <si>
-    <t>05/10/26 a 30/10/26</t>
-  </si>
-  <si>
     <t>16/09/26 a 30/09/26</t>
   </si>
   <si>
     <t>01/09/26 a 15/09/26</t>
   </si>
   <si>
-    <t>15335-4:SEBRAE</t>
-  </si>
-  <si>
     <t>13/08/26 a 31/08/26</t>
   </si>
   <si>
@@ -363,9 +354,6 @@
     <t>Geziel Sena Colares</t>
   </si>
   <si>
-    <t>15334-6: Empresa</t>
-  </si>
-  <si>
     <t>macroentrega_numero</t>
   </si>
   <si>
@@ -462,19 +450,22 @@
     <t>pago</t>
   </si>
   <si>
+    <t>15338-9:Conta EMBRAPII</t>
+  </si>
+  <si>
+    <t>15335-4: Conta SEBRAE</t>
+  </si>
+  <si>
+    <t>15334-6:Conta Empresa</t>
+  </si>
+  <si>
+    <t>total_parcelas</t>
+  </si>
+  <si>
+    <t>(Vários itens)</t>
+  </si>
+  <si>
     <t>a pagar</t>
-  </si>
-  <si>
-    <t>15338-9:Conta EMBRAPII</t>
-  </si>
-  <si>
-    <t>15335-4: Conta SEBRAE</t>
-  </si>
-  <si>
-    <t>15334-6:Conta Empresa</t>
-  </si>
-  <si>
-    <t>total_parcelas</t>
   </si>
 </sst>
 </file>
@@ -543,7 +534,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -565,12 +556,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -597,20 +582,23 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="IFAM" refreshedDate="46267.716177314818" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="116" xr:uid="{3DA39CE9-707E-45D2-B56A-E72A4666CE2D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Geziel Sena Colares" refreshedDate="46323.835406712962" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="116" xr:uid="{3DA39CE9-707E-45D2-B56A-E72A4666CE2D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:R1048576" sheet="relatorios-de-atividade"/>
   </cacheSource>
-  <cacheFields count="17">
+  <cacheFields count="18">
     <cacheField name="convenio_numero" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="projeto_conta" numFmtId="0">
-      <sharedItems containsBlank="1" count="4">
-        <s v="15334-6: Empresa"/>
-        <s v="15335-4:SEBRAE"/>
-        <s v="15338-9:EMBRAPII"/>
+      <sharedItems containsBlank="1" count="7">
+        <s v="15334-6:Conta Empresa"/>
+        <s v="15335-4: Conta SEBRAE"/>
+        <s v="15338-9:Conta EMBRAPII"/>
         <m/>
+        <s v="15334-6: Empresa" u="1"/>
+        <s v="15335-4:SEBRAE" u="1"/>
+        <s v="15338-9:EMBRAPII" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="bolsista_nome" numFmtId="0">
@@ -684,6 +672,9 @@
         <m/>
       </sharedItems>
     </cacheField>
+    <cacheField name="total_parcelas" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="8" maxValue="9"/>
+    </cacheField>
     <cacheField name="valor_parcela" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2000" maxValue="12000"/>
     </cacheField>
@@ -699,8 +690,8 @@
     <cacheField name="execucao_financeira" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
         <s v="pago"/>
-        <s v="a pagar"/>
         <m/>
+        <s v="a pagar" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -727,6 +718,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="160"/>
     <x v="0"/>
+    <n v="8"/>
     <n v="2800"/>
     <s v="25/06/26 a 14/07/26"/>
     <n v="20"/>
@@ -746,6 +738,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="160"/>
     <x v="1"/>
+    <n v="8"/>
     <n v="2800"/>
     <s v="15/07/26 a 31/07/26"/>
     <n v="20"/>
@@ -765,11 +758,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="160"/>
     <x v="2"/>
+    <n v="8"/>
     <n v="2800"/>
     <s v="03/08/26 a 31/08/26"/>
     <n v="20"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -784,11 +778,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="160"/>
     <x v="3"/>
+    <n v="8"/>
     <n v="2800"/>
     <s v="01/09/26 a 30/09/26"/>
     <n v="20"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -803,11 +798,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="160"/>
     <x v="4"/>
+    <n v="8"/>
     <n v="2800"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="20"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -822,11 +818,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="160"/>
     <x v="5"/>
+    <n v="8"/>
     <n v="2800"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="20"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -841,11 +838,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="160"/>
     <x v="6"/>
+    <n v="8"/>
     <n v="2800"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="20"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -860,11 +858,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="160"/>
     <x v="7"/>
+    <n v="8"/>
     <n v="2800"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="20"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -879,6 +878,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="25/06/26 a 14/07/26"/>
     <n v="40"/>
@@ -898,6 +898,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="15/07/26 a 31/07/26"/>
     <n v="40"/>
@@ -917,11 +918,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="03/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -936,11 +938,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -955,11 +958,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -974,11 +978,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -993,11 +998,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1012,11 +1018,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1031,11 +1038,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1050,6 +1058,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="25/06/26 a 14/07/26"/>
     <n v="40"/>
@@ -1069,6 +1078,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="15/07/26 a 31/07/26"/>
     <n v="40"/>
@@ -1088,11 +1098,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="03/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1107,11 +1118,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1126,11 +1138,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1145,11 +1158,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1164,11 +1178,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1183,11 +1198,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1202,11 +1218,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1221,6 +1238,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="25/06/26 a 14/07/26"/>
     <n v="40"/>
@@ -1240,6 +1258,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="15/07/26 a 31/07/26"/>
     <n v="40"/>
@@ -1259,11 +1278,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="03/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1278,11 +1298,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1297,11 +1318,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1316,11 +1338,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1335,11 +1358,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1354,11 +1378,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1373,11 +1398,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1392,6 +1418,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="25/06/26 a 14/07/26"/>
     <n v="40"/>
@@ -1411,6 +1438,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="15/07/26 a 31/07/26"/>
     <n v="40"/>
@@ -1430,11 +1458,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="03/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1449,11 +1478,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1468,11 +1498,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1487,11 +1518,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1506,11 +1538,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1525,11 +1558,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1544,11 +1578,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1563,6 +1598,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="25/06/26 a 14/07/26"/>
     <n v="40"/>
@@ -1582,6 +1618,7 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="15/07/26 a 31/07/26"/>
     <n v="40"/>
@@ -1601,11 +1638,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="03/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1620,11 +1658,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1639,11 +1678,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1658,11 +1698,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1677,11 +1718,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1696,11 +1738,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1715,11 +1758,12 @@
     <s v="25/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1734,6 +1778,7 @@
     <s v="13/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="7000"/>
     <s v="13/07/26 a 31/07/26"/>
     <n v="40"/>
@@ -1753,11 +1798,12 @@
     <s v="13/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="7000"/>
     <s v="01/08/26 a 15/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1772,11 +1818,12 @@
     <s v="13/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="7000"/>
     <s v="16/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1791,11 +1838,12 @@
     <s v="13/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="7000"/>
     <s v="01/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1810,11 +1858,12 @@
     <s v="13/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="7000"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1829,11 +1878,12 @@
     <s v="13/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="7000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1848,11 +1898,12 @@
     <s v="13/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="7000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1867,11 +1918,12 @@
     <s v="13/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="7000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1886,11 +1938,12 @@
     <s v="13/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="7000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1905,6 +1958,7 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="20/07/26 a 05/08/26"/>
     <n v="40"/>
@@ -1924,11 +1978,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="06/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1943,11 +1998,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/09/26 a 15/09/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1962,11 +2018,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="16/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -1981,11 +2038,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2000,11 +2058,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2019,11 +2078,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2038,11 +2098,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2057,11 +2118,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2076,6 +2138,7 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="320"/>
     <x v="0"/>
+    <n v="8"/>
     <n v="2125"/>
     <s v="20/07/26 a 05/08/26"/>
     <n v="40"/>
@@ -2095,11 +2158,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="320"/>
     <x v="1"/>
+    <n v="8"/>
     <n v="2125"/>
     <s v="06/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2114,11 +2178,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="320"/>
     <x v="2"/>
+    <n v="8"/>
     <n v="2125"/>
     <s v="01/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2133,11 +2198,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="320"/>
     <x v="3"/>
+    <n v="8"/>
     <n v="2125"/>
-    <s v="01/10/26 a 30/10/26"/>
+    <s v="01/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2152,11 +2218,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="320"/>
     <x v="4"/>
+    <n v="8"/>
     <n v="2125"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2171,11 +2238,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="320"/>
     <x v="5"/>
+    <n v="8"/>
     <n v="2125"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2190,11 +2258,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="320"/>
     <x v="6"/>
+    <n v="8"/>
     <n v="2125"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2209,11 +2278,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="320"/>
     <x v="7"/>
+    <n v="8"/>
     <n v="2125"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2228,6 +2298,7 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="20/07/26 a 05/08/26"/>
     <n v="40"/>
@@ -2247,11 +2318,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="06/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2266,11 +2338,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/09/26 a 15/09/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2285,11 +2358,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="16/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2304,11 +2378,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2323,11 +2398,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2342,11 +2418,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2361,11 +2438,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2380,11 +2458,12 @@
     <s v="20/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="2000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2399,6 +2478,7 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="27/07/26 a 12/08/26"/>
     <n v="40"/>
@@ -2418,11 +2498,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="13/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2437,11 +2518,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/09/26 a 15/09/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2456,11 +2538,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="16/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2475,11 +2558,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="5000"/>
-    <s v="05/10/26 a 30/10/26"/>
+    <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2494,11 +2578,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2513,11 +2598,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2532,11 +2618,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2551,11 +2638,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2570,6 +2658,7 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="27/07/26 a 12/08/26"/>
     <n v="40"/>
@@ -2589,11 +2678,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="13/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2608,11 +2698,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/09/26 a 15/09/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2627,11 +2718,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="16/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2646,11 +2738,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="5000"/>
-    <s v="05/10/26 a 30/10/26"/>
+    <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2665,11 +2758,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2684,11 +2778,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2703,11 +2798,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2722,11 +2818,12 @@
     <s v="27/07/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="5000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2741,6 +2838,7 @@
     <s v="01/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="0"/>
+    <n v="9"/>
     <n v="12000"/>
     <s v="01/06/26 a 31/06/26"/>
     <n v="40"/>
@@ -2760,6 +2858,7 @@
     <s v="01/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="1"/>
+    <n v="9"/>
     <n v="12000"/>
     <s v="01/07/26 a 31/07/26"/>
     <n v="40"/>
@@ -2779,11 +2878,12 @@
     <s v="01/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="2"/>
+    <n v="9"/>
     <n v="12000"/>
     <s v="03/08/26 a 31/08/26"/>
     <n v="40"/>
     <n v="1"/>
-    <x v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2798,11 +2898,12 @@
     <s v="01/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="3"/>
+    <n v="9"/>
     <n v="12000"/>
     <s v="01/09/26 a 30/09/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2817,11 +2918,12 @@
     <s v="01/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="4"/>
+    <n v="9"/>
     <n v="12000"/>
     <s v="01/10/26 a 30/10/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2836,11 +2938,12 @@
     <s v="01/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="5"/>
+    <n v="9"/>
     <n v="12000"/>
     <s v="02/11/26 a 30/11/26"/>
     <n v="40"/>
     <n v="2"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2855,11 +2958,12 @@
     <s v="01/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="6"/>
+    <n v="9"/>
     <n v="12000"/>
     <s v="01/12/26 a 31/12/26"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2874,11 +2978,12 @@
     <s v="01/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="7"/>
+    <n v="9"/>
     <n v="12000"/>
     <s v="04/01/27 a 29/01/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="0002/2026"/>
@@ -2893,11 +2998,12 @@
     <s v="01/06/2026 a 28/02/2027"/>
     <n v="360"/>
     <x v="8"/>
+    <n v="9"/>
     <n v="12000"/>
     <s v="01/02/27 a 26/02/27"/>
     <n v="40"/>
     <n v="3"/>
-    <x v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <m/>
@@ -2916,22 +3022,26 @@
     <m/>
     <m/>
     <m/>
-    <x v="2"/>
+    <m/>
+    <x v="1"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A830E048-53DB-475F-914B-949B73307877}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:D34" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="17">
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="18">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="5">
+      <items count="8">
+        <item m="1" x="4"/>
+        <item m="1" x="5"/>
+        <item m="1" x="6"/>
+        <item x="3"/>
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
-        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2995,15 +3105,16 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
-        <item x="1"/>
+        <item m="1" x="2"/>
         <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3013,94 +3124,7 @@
     <field x="7"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="30">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="2">
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="2">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="2">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="2">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="2">
-      <x v="12"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="2">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-    </i>
-    <i r="2">
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="2">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
+  <rowItems count="1">
     <i t="grand">
       <x/>
     </i>
@@ -3108,22 +3132,16 @@
   <colFields count="1">
     <field x="11"/>
   </colFields>
-  <colItems count="3">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
+  <colItems count="1">
     <i t="grand">
       <x/>
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="16" hier="-1"/>
+    <pageField fld="17" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Soma de valor_parcela" fld="12" baseField="1" baseItem="2" numFmtId="44"/>
+    <dataField name="Soma de valor_parcela" fld="13" baseField="1" baseItem="2" numFmtId="44"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -3457,112 +3475,112 @@
   <dimension ref="A1:R116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" style="1" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="31" style="1" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.85546875" style="1" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="26.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="24.5703125" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="24.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="26" style="1" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K2" s="1">
         <v>160</v>
@@ -3577,7 +3595,7 @@
         <v>2800</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P2" s="1">
         <v>20</v>
@@ -3586,39 +3604,39 @@
         <v>1</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K3" s="1">
         <v>160</v>
@@ -3633,7 +3651,7 @@
         <v>2800</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P3" s="1">
         <v>20</v>
@@ -3642,39 +3660,39 @@
         <v>1</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K4" s="1">
         <v>160</v>
@@ -3689,7 +3707,7 @@
         <v>2800</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P4" s="1">
         <v>20</v>
@@ -3698,54 +3716,54 @@
         <v>1</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>102</v>
+        <v>136</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>96</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K5" s="11">
+        <v>59</v>
+      </c>
+      <c r="K5" s="9">
         <v>160</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="9">
         <v>4</v>
       </c>
       <c r="M5" s="1">
         <v>8</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="10">
         <v>2800</v>
       </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
+      <c r="O5" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="P5" s="1">
         <v>20</v>
@@ -3753,40 +3771,40 @@
       <c r="Q5" s="1">
         <v>2</v>
       </c>
-      <c r="R5" s="11" t="s">
-        <v>138</v>
+      <c r="R5" s="9" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K6" s="1">
         <v>160</v>
@@ -3801,7 +3819,7 @@
         <v>2800</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P6" s="1">
         <v>20</v>
@@ -3809,37 +3827,40 @@
       <c r="Q6" s="1">
         <v>2</v>
       </c>
+      <c r="R6" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K7" s="1">
         <v>160</v>
@@ -3854,7 +3875,7 @@
         <v>2800</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P7" s="1">
         <v>20</v>
@@ -3865,34 +3886,34 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K8" s="1">
         <v>160</v>
@@ -3907,7 +3928,7 @@
         <v>2800</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P8" s="1">
         <v>20</v>
@@ -3918,34 +3939,34 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K9" s="1">
         <v>160</v>
@@ -3960,7 +3981,7 @@
         <v>2800</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P9" s="1">
         <v>20</v>
@@ -3971,34 +3992,34 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
         <v>548625239</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K10" s="1">
         <v>360</v>
@@ -4013,7 +4034,7 @@
         <v>5000</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P10" s="1">
         <v>40</v>
@@ -4022,39 +4043,39 @@
         <v>1</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
         <v>548625239</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K11" s="1">
         <v>360</v>
@@ -4069,7 +4090,7 @@
         <v>5000</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P11" s="1">
         <v>40</v>
@@ -4078,39 +4099,39 @@
         <v>1</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
         <v>548625239</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K12" s="1">
         <v>360</v>
@@ -4125,7 +4146,7 @@
         <v>5000</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P12" s="1">
         <v>40</v>
@@ -4134,39 +4155,39 @@
         <v>1</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
         <v>548625239</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K13" s="1">
         <v>360</v>
@@ -4181,7 +4202,7 @@
         <v>5000</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P13" s="1">
         <v>40</v>
@@ -4190,39 +4211,39 @@
         <v>2</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1">
         <v>548625239</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K14" s="1">
         <v>360</v>
@@ -4237,7 +4258,7 @@
         <v>5000</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P14" s="1">
         <v>40</v>
@@ -4245,37 +4266,40 @@
       <c r="Q14" s="1">
         <v>2</v>
       </c>
+      <c r="R14" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1">
         <v>548625239</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K15" s="1">
         <v>360</v>
@@ -4290,7 +4314,7 @@
         <v>5000</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P15" s="1">
         <v>40</v>
@@ -4301,34 +4325,34 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1">
         <v>548625239</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K16" s="1">
         <v>360</v>
@@ -4343,7 +4367,7 @@
         <v>5000</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P16" s="1">
         <v>40</v>
@@ -4354,34 +4378,34 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E17" s="1">
         <v>548625239</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K17" s="1">
         <v>360</v>
@@ -4396,7 +4420,7 @@
         <v>5000</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P17" s="1">
         <v>40</v>
@@ -4407,34 +4431,34 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E18" s="1">
         <v>548625239</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K18" s="1">
         <v>360</v>
@@ -4460,34 +4484,34 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E19" s="1">
         <v>209299274</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K19" s="1">
         <v>360</v>
@@ -4502,7 +4526,7 @@
         <v>2000</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P19" s="1">
         <v>40</v>
@@ -4511,39 +4535,39 @@
         <v>1</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E20" s="1">
         <v>209299274</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K20" s="1">
         <v>360</v>
@@ -4558,7 +4582,7 @@
         <v>2000</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P20" s="1">
         <v>40</v>
@@ -4567,39 +4591,39 @@
         <v>1</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E21" s="1">
         <v>209299274</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K21" s="1">
         <v>360</v>
@@ -4614,7 +4638,7 @@
         <v>2000</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P21" s="1">
         <v>40</v>
@@ -4623,39 +4647,39 @@
         <v>1</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E22" s="1">
         <v>209299274</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K22" s="1">
         <v>360</v>
@@ -4670,7 +4694,7 @@
         <v>2000</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P22" s="1">
         <v>40</v>
@@ -4679,39 +4703,39 @@
         <v>2</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E23" s="1">
         <v>209299274</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K23" s="1">
         <v>360</v>
@@ -4726,7 +4750,7 @@
         <v>2000</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P23" s="1">
         <v>40</v>
@@ -4734,37 +4758,40 @@
       <c r="Q23" s="1">
         <v>2</v>
       </c>
+      <c r="R23" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E24" s="1">
         <v>209299274</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K24" s="1">
         <v>360</v>
@@ -4779,7 +4806,7 @@
         <v>2000</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P24" s="1">
         <v>40</v>
@@ -4790,34 +4817,34 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E25" s="1">
         <v>209299274</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K25" s="1">
         <v>360</v>
@@ -4832,7 +4859,7 @@
         <v>2000</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P25" s="1">
         <v>40</v>
@@ -4843,34 +4870,34 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E26" s="1">
         <v>209299274</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K26" s="1">
         <v>360</v>
@@ -4885,7 +4912,7 @@
         <v>2000</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P26" s="1">
         <v>40</v>
@@ -4896,34 +4923,34 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E27" s="1">
         <v>209299274</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K27" s="1">
         <v>360</v>
@@ -4949,34 +4976,34 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K28" s="1">
         <v>360</v>
@@ -4991,7 +5018,7 @@
         <v>2000</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P28" s="1">
         <v>40</v>
@@ -5000,39 +5027,39 @@
         <v>1</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K29" s="1">
         <v>360</v>
@@ -5047,7 +5074,7 @@
         <v>2000</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P29" s="1">
         <v>40</v>
@@ -5056,39 +5083,39 @@
         <v>1</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K30" s="1">
         <v>360</v>
@@ -5103,7 +5130,7 @@
         <v>2000</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P30" s="1">
         <v>40</v>
@@ -5112,39 +5139,39 @@
         <v>1</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K31" s="1">
         <v>360</v>
@@ -5159,7 +5186,7 @@
         <v>2000</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P31" s="1">
         <v>40</v>
@@ -5168,39 +5195,39 @@
         <v>2</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K32" s="1">
         <v>360</v>
@@ -5215,7 +5242,7 @@
         <v>2000</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P32" s="1">
         <v>40</v>
@@ -5223,37 +5250,40 @@
       <c r="Q32" s="1">
         <v>2</v>
       </c>
+      <c r="R32" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K33" s="1">
         <v>360</v>
@@ -5268,7 +5298,7 @@
         <v>2000</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P33" s="1">
         <v>40</v>
@@ -5279,34 +5309,34 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K34" s="1">
         <v>360</v>
@@ -5321,7 +5351,7 @@
         <v>2000</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P34" s="1">
         <v>40</v>
@@ -5332,34 +5362,34 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K35" s="1">
         <v>360</v>
@@ -5374,7 +5404,7 @@
         <v>2000</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P35" s="1">
         <v>40</v>
@@ -5385,34 +5415,34 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K36" s="1">
         <v>360</v>
@@ -5438,34 +5468,34 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E37" s="1">
         <v>33784396</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K37" s="1">
         <v>360</v>
@@ -5480,7 +5510,7 @@
         <v>2000</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P37" s="1">
         <v>40</v>
@@ -5489,39 +5519,39 @@
         <v>1</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E38" s="1">
         <v>33784396</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K38" s="1">
         <v>360</v>
@@ -5536,7 +5566,7 @@
         <v>2000</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P38" s="1">
         <v>40</v>
@@ -5545,39 +5575,39 @@
         <v>1</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E39" s="1">
         <v>33784396</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K39" s="1">
         <v>360</v>
@@ -5592,7 +5622,7 @@
         <v>2000</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P39" s="1">
         <v>40</v>
@@ -5601,39 +5631,39 @@
         <v>1</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E40" s="1">
         <v>33784396</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K40" s="1">
         <v>360</v>
@@ -5648,7 +5678,7 @@
         <v>2000</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P40" s="1">
         <v>40</v>
@@ -5657,39 +5687,39 @@
         <v>2</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E41" s="1">
         <v>33784396</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K41" s="1">
         <v>360</v>
@@ -5704,7 +5734,7 @@
         <v>2000</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P41" s="1">
         <v>40</v>
@@ -5712,37 +5742,40 @@
       <c r="Q41" s="1">
         <v>2</v>
       </c>
+      <c r="R41" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E42" s="1">
         <v>33784396</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K42" s="1">
         <v>360</v>
@@ -5757,7 +5790,7 @@
         <v>2000</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P42" s="1">
         <v>40</v>
@@ -5768,34 +5801,34 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E43" s="1">
         <v>33784396</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K43" s="1">
         <v>360</v>
@@ -5810,7 +5843,7 @@
         <v>2000</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P43" s="1">
         <v>40</v>
@@ -5821,34 +5854,34 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E44" s="1">
         <v>33784396</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K44" s="1">
         <v>360</v>
@@ -5863,7 +5896,7 @@
         <v>2000</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P44" s="1">
         <v>40</v>
@@ -5874,34 +5907,34 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E45" s="1">
         <v>33784396</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K45" s="1">
         <v>360</v>
@@ -5927,34 +5960,34 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K46" s="1">
         <v>360</v>
@@ -5969,7 +6002,7 @@
         <v>2000</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P46" s="1">
         <v>40</v>
@@ -5978,39 +6011,39 @@
         <v>1</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K47" s="1">
         <v>360</v>
@@ -6025,7 +6058,7 @@
         <v>2000</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P47" s="1">
         <v>40</v>
@@ -6034,39 +6067,39 @@
         <v>1</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K48" s="1">
         <v>360</v>
@@ -6081,7 +6114,7 @@
         <v>2000</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P48" s="1">
         <v>40</v>
@@ -6090,39 +6123,39 @@
         <v>1</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K49" s="1">
         <v>360</v>
@@ -6137,7 +6170,7 @@
         <v>2000</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P49" s="1">
         <v>40</v>
@@ -6146,39 +6179,39 @@
         <v>2</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K50" s="1">
         <v>360</v>
@@ -6193,7 +6226,7 @@
         <v>2000</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P50" s="1">
         <v>40</v>
@@ -6201,37 +6234,40 @@
       <c r="Q50" s="1">
         <v>2</v>
       </c>
+      <c r="R50" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K51" s="1">
         <v>360</v>
@@ -6246,7 +6282,7 @@
         <v>2000</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P51" s="1">
         <v>40</v>
@@ -6257,34 +6293,34 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K52" s="1">
         <v>360</v>
@@ -6299,7 +6335,7 @@
         <v>2000</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P52" s="1">
         <v>40</v>
@@ -6310,34 +6346,34 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K53" s="1">
         <v>360</v>
@@ -6352,7 +6388,7 @@
         <v>2000</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P53" s="1">
         <v>40</v>
@@ -6363,34 +6399,34 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K54" s="1">
         <v>360</v>
@@ -6416,34 +6452,34 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K55" s="1">
         <v>360</v>
@@ -6458,7 +6494,7 @@
         <v>7000</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P55" s="1">
         <v>40</v>
@@ -6467,39 +6503,39 @@
         <v>1</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K56" s="1">
         <v>360</v>
@@ -6514,7 +6550,7 @@
         <v>7000</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P56" s="1">
         <v>40</v>
@@ -6523,39 +6559,39 @@
         <v>1</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K57" s="1">
         <v>360</v>
@@ -6570,7 +6606,7 @@
         <v>7000</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P57" s="1">
         <v>40</v>
@@ -6579,39 +6615,39 @@
         <v>1</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K58" s="1">
         <v>360</v>
@@ -6626,7 +6662,7 @@
         <v>7000</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P58" s="1">
         <v>40</v>
@@ -6635,39 +6671,39 @@
         <v>2</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K59" s="1">
         <v>360</v>
@@ -6682,7 +6718,7 @@
         <v>7000</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P59" s="1">
         <v>40</v>
@@ -6690,37 +6726,40 @@
       <c r="Q59" s="1">
         <v>2</v>
       </c>
+      <c r="R59" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K60" s="1">
         <v>360</v>
@@ -6735,7 +6774,7 @@
         <v>7000</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P60" s="1">
         <v>40</v>
@@ -6746,34 +6785,34 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K61" s="1">
         <v>360</v>
@@ -6788,7 +6827,7 @@
         <v>7000</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P61" s="1">
         <v>40</v>
@@ -6799,34 +6838,34 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K62" s="1">
         <v>360</v>
@@ -6841,7 +6880,7 @@
         <v>7000</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P62" s="1">
         <v>40</v>
@@ -6852,34 +6891,34 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K63" s="1">
         <v>360</v>
@@ -6905,34 +6944,34 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K64" s="1">
         <v>360</v>
@@ -6947,7 +6986,7 @@
         <v>5000</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P64" s="1">
         <v>40</v>
@@ -6956,39 +6995,39 @@
         <v>1</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K65" s="1">
         <v>360</v>
@@ -7003,7 +7042,7 @@
         <v>5000</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P65" s="1">
         <v>40</v>
@@ -7012,39 +7051,39 @@
         <v>1</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K66" s="1">
         <v>360</v>
@@ -7059,7 +7098,7 @@
         <v>5000</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P66" s="1">
         <v>40</v>
@@ -7068,39 +7107,39 @@
         <v>1</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K67" s="1">
         <v>360</v>
@@ -7115,7 +7154,7 @@
         <v>5000</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P67" s="1">
         <v>40</v>
@@ -7124,39 +7163,39 @@
         <v>2</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K68" s="1">
         <v>360</v>
@@ -7171,7 +7210,7 @@
         <v>5000</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P68" s="1">
         <v>40</v>
@@ -7179,37 +7218,40 @@
       <c r="Q68" s="1">
         <v>2</v>
       </c>
+      <c r="R68" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K69" s="1">
         <v>360</v>
@@ -7224,7 +7266,7 @@
         <v>5000</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P69" s="1">
         <v>40</v>
@@ -7235,34 +7277,34 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K70" s="1">
         <v>360</v>
@@ -7277,7 +7319,7 @@
         <v>5000</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P70" s="1">
         <v>40</v>
@@ -7288,34 +7330,34 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K71" s="1">
         <v>360</v>
@@ -7330,7 +7372,7 @@
         <v>5000</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P71" s="1">
         <v>40</v>
@@ -7341,34 +7383,34 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K72" s="1">
         <v>360</v>
@@ -7394,34 +7436,34 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K73" s="1">
         <v>320</v>
@@ -7436,7 +7478,7 @@
         <v>2125</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P73" s="1">
         <v>40</v>
@@ -7445,39 +7487,39 @@
         <v>1</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K74" s="1">
         <v>320</v>
@@ -7492,7 +7534,7 @@
         <v>2125</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P74" s="1">
         <v>40</v>
@@ -7501,39 +7543,39 @@
         <v>1</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K75" s="1">
         <v>320</v>
@@ -7548,7 +7590,7 @@
         <v>2125</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P75" s="1">
         <v>40</v>
@@ -7557,39 +7599,39 @@
         <v>1</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K76" s="1">
         <v>320</v>
@@ -7604,7 +7646,7 @@
         <v>2125</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P76" s="1">
         <v>40</v>
@@ -7612,37 +7654,40 @@
       <c r="Q76" s="1">
         <v>2</v>
       </c>
+      <c r="R76" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K77" s="1">
         <v>320</v>
@@ -7657,7 +7702,7 @@
         <v>2125</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="P77" s="1">
         <v>40</v>
@@ -7668,34 +7713,34 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K78" s="1">
         <v>320</v>
@@ -7710,7 +7755,7 @@
         <v>2125</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P78" s="1">
         <v>40</v>
@@ -7721,34 +7766,34 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K79" s="1">
         <v>320</v>
@@ -7763,7 +7808,7 @@
         <v>2125</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P79" s="1">
         <v>40</v>
@@ -7774,34 +7819,34 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K80" s="1">
         <v>320</v>
@@ -7816,7 +7861,7 @@
         <v>2125</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P80" s="1">
         <v>40</v>
@@ -7827,34 +7872,34 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E81" s="1">
         <v>9601144</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K81" s="1">
         <v>360</v>
@@ -7869,7 +7914,7 @@
         <v>2000</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P81" s="1">
         <v>40</v>
@@ -7878,39 +7923,39 @@
         <v>1</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E82" s="1">
         <v>9601144</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K82" s="1">
         <v>360</v>
@@ -7925,7 +7970,7 @@
         <v>2000</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P82" s="1">
         <v>40</v>
@@ -7934,39 +7979,39 @@
         <v>1</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E83" s="1">
         <v>9601144</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K83" s="1">
         <v>360</v>
@@ -7981,7 +8026,7 @@
         <v>2000</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P83" s="1">
         <v>40</v>
@@ -7990,39 +8035,39 @@
         <v>1</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E84" s="1">
         <v>9601144</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K84" s="1">
         <v>360</v>
@@ -8037,7 +8082,7 @@
         <v>2000</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P84" s="1">
         <v>40</v>
@@ -8046,39 +8091,39 @@
         <v>2</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E85" s="1">
         <v>9601144</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K85" s="1">
         <v>360</v>
@@ -8093,7 +8138,7 @@
         <v>2000</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P85" s="1">
         <v>40</v>
@@ -8101,37 +8146,40 @@
       <c r="Q85" s="1">
         <v>2</v>
       </c>
+      <c r="R85" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E86" s="1">
         <v>9601144</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K86" s="1">
         <v>360</v>
@@ -8146,7 +8194,7 @@
         <v>2000</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P86" s="1">
         <v>40</v>
@@ -8157,34 +8205,34 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E87" s="1">
         <v>9601144</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K87" s="1">
         <v>360</v>
@@ -8199,7 +8247,7 @@
         <v>2000</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P87" s="1">
         <v>40</v>
@@ -8210,34 +8258,34 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E88" s="1">
         <v>9601144</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K88" s="1">
         <v>360</v>
@@ -8252,7 +8300,7 @@
         <v>2000</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P88" s="1">
         <v>40</v>
@@ -8263,34 +8311,34 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E89" s="1">
         <v>9601144</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K89" s="1">
         <v>360</v>
@@ -8316,31 +8364,31 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E90" s="1">
         <v>19274254</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>1</v>
@@ -8358,7 +8406,7 @@
         <v>5000</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P90" s="1">
         <v>40</v>
@@ -8367,36 +8415,36 @@
         <v>1</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E91" s="1">
         <v>19274254</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>1</v>
@@ -8414,7 +8462,7 @@
         <v>5000</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P91" s="1">
         <v>40</v>
@@ -8423,36 +8471,36 @@
         <v>1</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E92" s="1">
         <v>19274254</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>1</v>
@@ -8470,7 +8518,7 @@
         <v>5000</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P92" s="1">
         <v>40</v>
@@ -8479,36 +8527,36 @@
         <v>1</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E93" s="1">
         <v>19274254</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>1</v>
@@ -8526,7 +8574,7 @@
         <v>5000</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P93" s="1">
         <v>40</v>
@@ -8535,36 +8583,36 @@
         <v>2</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E94" s="1">
         <v>19274254</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>1</v>
@@ -8582,7 +8630,7 @@
         <v>5000</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="P94" s="1">
         <v>40</v>
@@ -8590,34 +8638,37 @@
       <c r="Q94" s="1">
         <v>2</v>
       </c>
+      <c r="R94" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E95" s="1">
         <v>19274254</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>1</v>
@@ -8635,7 +8686,7 @@
         <v>5000</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P95" s="1">
         <v>40</v>
@@ -8646,31 +8697,31 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E96" s="1">
         <v>19274254</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>1</v>
@@ -8688,7 +8739,7 @@
         <v>5000</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P96" s="1">
         <v>40</v>
@@ -8699,31 +8750,31 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E97" s="1">
         <v>19274254</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>1</v>
@@ -8741,7 +8792,7 @@
         <v>5000</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P97" s="1">
         <v>40</v>
@@ -8752,31 +8803,31 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E98" s="1">
         <v>19274254</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>1</v>
@@ -8805,10 +8856,10 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>8</v>
@@ -8847,7 +8898,7 @@
         <v>5000</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P99" s="1">
         <v>40</v>
@@ -8856,15 +8907,15 @@
         <v>1</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>8</v>
@@ -8903,7 +8954,7 @@
         <v>5000</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P100" s="1">
         <v>40</v>
@@ -8912,15 +8963,15 @@
         <v>1</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>8</v>
@@ -8959,7 +9010,7 @@
         <v>5000</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P101" s="1">
         <v>40</v>
@@ -8968,15 +9019,15 @@
         <v>1</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>8</v>
@@ -9015,7 +9066,7 @@
         <v>5000</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P102" s="1">
         <v>40</v>
@@ -9024,15 +9075,15 @@
         <v>2</v>
       </c>
       <c r="R102" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>8</v>
@@ -9071,7 +9122,7 @@
         <v>5000</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="P103" s="1">
         <v>40</v>
@@ -9079,13 +9130,16 @@
       <c r="Q103" s="1">
         <v>2</v>
       </c>
+      <c r="R103" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>8</v>
@@ -9124,7 +9178,7 @@
         <v>5000</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P104" s="1">
         <v>40</v>
@@ -9135,10 +9189,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>8</v>
@@ -9177,7 +9231,7 @@
         <v>5000</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P105" s="1">
         <v>40</v>
@@ -9188,10 +9242,10 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>8</v>
@@ -9230,7 +9284,7 @@
         <v>5000</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P106" s="1">
         <v>40</v>
@@ -9241,10 +9295,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>8</v>
@@ -9294,34 +9348,34 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C108" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E108" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J108" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="K108" s="1">
         <v>360</v>
@@ -9336,7 +9390,7 @@
         <v>12000</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="P108" s="1">
         <v>40</v>
@@ -9345,39 +9399,39 @@
         <v>1</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C109" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E109" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J109" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="K109" s="1">
         <v>360</v>
@@ -9392,7 +9446,7 @@
         <v>12000</v>
       </c>
       <c r="O109" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="P109" s="1">
         <v>40</v>
@@ -9401,39 +9455,39 @@
         <v>1</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C110" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E110" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J110" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="K110" s="1">
         <v>360</v>
@@ -9448,7 +9502,7 @@
         <v>12000</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P110" s="1">
         <v>40</v>
@@ -9457,39 +9511,39 @@
         <v>1</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C111" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E111" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J111" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="K111" s="1">
         <v>360</v>
@@ -9504,7 +9558,7 @@
         <v>12000</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P111" s="1">
         <v>40</v>
@@ -9513,39 +9567,39 @@
         <v>2</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C112" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E112" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J112" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="K112" s="1">
         <v>360</v>
@@ -9560,7 +9614,7 @@
         <v>12000</v>
       </c>
       <c r="O112" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P112" s="1">
         <v>40</v>
@@ -9568,37 +9622,40 @@
       <c r="Q112" s="1">
         <v>2</v>
       </c>
+      <c r="R112" s="1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C113" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D113" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E113" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J113" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="K113" s="1">
         <v>360</v>
@@ -9613,7 +9670,7 @@
         <v>12000</v>
       </c>
       <c r="O113" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P113" s="1">
         <v>40</v>
@@ -9624,34 +9681,34 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C114" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E114" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J114" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="K114" s="1">
         <v>360</v>
@@ -9666,7 +9723,7 @@
         <v>12000</v>
       </c>
       <c r="O114" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P114" s="1">
         <v>40</v>
@@ -9677,34 +9734,34 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C115" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E115" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J115" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="K115" s="1">
         <v>360</v>
@@ -9719,7 +9776,7 @@
         <v>12000</v>
       </c>
       <c r="O115" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P115" s="1">
         <v>40</v>
@@ -9730,34 +9787,34 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C116" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E116" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J116" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="K116" s="1">
         <v>360</v>
@@ -9816,10 +9873,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F55A53B-8525-4418-BF70-6CF5583A54B5}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -9947,405 +10004,35 @@
     <col min="128" max="128" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B5" s="8"/>
-      <c r="C5" s="8">
-        <v>2800</v>
-      </c>
-      <c r="D5" s="8">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8">
-        <v>2800</v>
-      </c>
-      <c r="D6" s="8">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8">
-        <v>2800</v>
-      </c>
-      <c r="D7" s="8">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="8">
-        <v>24000</v>
-      </c>
-      <c r="C8" s="8">
-        <v>28000</v>
-      </c>
-      <c r="D8" s="8">
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D9" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D10" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D11" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D12" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="8">
-        <v>2000</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="8">
-        <v>2000</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8">
-        <v>5000</v>
-      </c>
-      <c r="D15" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8">
-        <v>5000</v>
-      </c>
-      <c r="D16" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="8">
-        <v>5000</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="8">
-        <v>5000</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="8">
-        <v>7000</v>
-      </c>
-      <c r="C19" s="8">
-        <v>7000</v>
-      </c>
-      <c r="D19" s="8">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="8">
-        <v>7000</v>
-      </c>
-      <c r="C20" s="8">
-        <v>7000</v>
-      </c>
-      <c r="D20" s="8">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8">
-        <v>12000</v>
-      </c>
-      <c r="D21" s="8">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8">
-        <v>12000</v>
-      </c>
-      <c r="D22" s="8">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="8">
-        <v>5000</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="8">
-        <v>5000</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="8">
-        <v>5000</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="8">
-        <v>5000</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="8">
-        <v>2125</v>
-      </c>
-      <c r="C27" s="8">
-        <v>4000</v>
-      </c>
-      <c r="D27" s="8">
-        <v>6125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D28" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D29" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D30" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D31" s="8">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="8">
-        <v>2125</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="8">
-        <v>2125</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B34" s="8">
-        <v>26125</v>
-      </c>
-      <c r="C34" s="8">
-        <v>34800</v>
-      </c>
-      <c r="D34" s="8">
-        <v>60925</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
